--- a/ckanext/lhm/schemas/template_master.xlsx
+++ b/ckanext/lhm/schemas/template_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\home\mb\p2\ckanext-lhm\ckanext\lhm\schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9BD412-5589-48DE-A66A-0C1215D87B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC350C4-34D8-48FB-A33A-6762A274E3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1248" yWindow="468" windowWidth="21792" windowHeight="11772" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadaten" sheetId="1" r:id="rId1"/>
@@ -773,7 +773,7 @@
     <t>Bedeutung</t>
   </si>
   <si>
-    <t>1.2.5.</t>
+    <t>1.3.1.</t>
   </si>
 </sst>
 </file>

--- a/ckanext/lhm/schemas/template_master.xlsx
+++ b/ckanext/lhm/schemas/template_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\home\mb\p2\ckanext-lhm\ckanext\lhm\schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9BD412-5589-48DE-A66A-0C1215D87B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B0AE3D-13EF-43EF-9195-77E14740007F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1248" yWindow="468" windowWidth="21792" windowHeight="11772" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadaten" sheetId="1" r:id="rId1"/>
@@ -773,7 +773,7 @@
     <t>Bedeutung</t>
   </si>
   <si>
-    <t>1.2.5.</t>
+    <t>1.3.1.</t>
   </si>
 </sst>
 </file>

--- a/ckanext/lhm/schemas/template_master.xlsx
+++ b/ckanext/lhm/schemas/template_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\home\mb\p2\ckanext-lhm\ckanext\lhm\schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC350C4-34D8-48FB-A33A-6762A274E3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE41826-D22D-477B-9CB4-42AA63F6D747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
   </bookViews>
@@ -306,9 +306,6 @@
     <t>_id</t>
   </si>
   <si>
-    <t>ArcGIS Kartenservice</t>
-  </si>
-  <si>
     <t>URL</t>
   </si>
   <si>
@@ -352,9 +349,6 @@
   </si>
   <si>
     <t>XML/GML</t>
-  </si>
-  <si>
-    <t>Link</t>
   </si>
   <si>
     <t>URL / Datei</t>
@@ -773,7 +767,13 @@
     <t>Bedeutung</t>
   </si>
   <si>
-    <t>1.3.1.</t>
+    <t>1.3.2.</t>
+  </si>
+  <si>
+    <t>ArcGIS Map Service</t>
+  </si>
+  <si>
+    <t>ArcGIS Feature Service</t>
   </si>
 </sst>
 </file>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="12"/>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B4" s="21"/>
       <c r="C4" s="12"/>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="24"/>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="16" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="22"/>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="12"/>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="12"/>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="12"/>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="12"/>
@@ -1664,7 +1664,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B18" s="22"/>
       <c r="C18" s="12"/>
@@ -1679,7 +1679,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B19" s="22"/>
       <c r="C19" s="12"/>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="12"/>
@@ -1709,7 +1709,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="16" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="12"/>
@@ -1724,7 +1724,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="16" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="12"/>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="12"/>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B25" s="22"/>
       <c r="C25" s="12"/>
@@ -1784,7 +1784,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B26" s="22"/>
       <c r="C26" s="12"/>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="25"/>
@@ -1814,7 +1814,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="25"/>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="18" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="12"/>
@@ -1845,7 +1845,7 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B30" s="26"/>
       <c r="C30" s="12"/>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="14" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B32" s="27"/>
       <c r="C32" s="12"/>
@@ -1893,10 +1893,10 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="14" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="30" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B38" s="31"/>
       <c r="C38" s="31"/>
@@ -2037,10 +2037,10 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="28" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>82</v>
@@ -2052,7 +2052,7 @@
         <v>81</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2082,13 +2082,13 @@
         <v>85</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>61</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -2113,16 +2113,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="C1" s="28" t="s">
-        <v>89</v>
-      </c>
       <c r="D1" s="28" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2156,7 +2156,7 @@
     <col min="15" max="15" width="14.5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="27.3984375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="22.19921875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="23.796875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="27.3984375" bestFit="1" customWidth="1"/>
@@ -2165,70 +2165,70 @@
   <sheetData>
     <row r="1" spans="1:22" s="1" customFormat="1">
       <c r="A1" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="O1" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="R1" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="N1" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>229</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:22">
@@ -2239,60 +2239,60 @@
         <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>79</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>80</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -2303,64 +2303,64 @@
         <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -2371,31 +2371,31 @@
         <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>84</v>
@@ -2404,19 +2404,19 @@
         <v>84</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>84</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -2427,34 +2427,34 @@
         <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -2465,34 +2465,34 @@
         <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -2503,28 +2503,28 @@
         <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -2535,28 +2535,28 @@
         <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -2567,17 +2567,17 @@
         <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E9" s="1"/>
       <c r="G9" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>86</v>
+        <v>235</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -2588,18 +2588,18 @@
         <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E10" s="1"/>
       <c r="G10" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K10" s="15"/>
       <c r="R10" s="2" t="s">
-        <v>87</v>
+        <v>236</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -2610,18 +2610,18 @@
         <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E11" s="1"/>
       <c r="G11" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K11" s="15"/>
       <c r="R11" s="2" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -2632,12 +2632,12 @@
         <v>33</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E12" s="1"/>
       <c r="K12" s="15"/>
       <c r="U12" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2648,7 +2648,7 @@
         <v>34</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E13" s="1"/>
       <c r="K13" s="15"/>
@@ -2661,7 +2661,7 @@
         <v>35</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E14" s="1"/>
       <c r="K14" s="15"/>
@@ -2674,7 +2674,7 @@
         <v>36</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E15" s="1"/>
       <c r="K15" s="15"/>
@@ -2687,7 +2687,7 @@
         <v>37</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E16" s="1"/>
       <c r="K16" s="15"/>
@@ -2700,7 +2700,7 @@
         <v>38</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E17" s="1"/>
       <c r="K17" s="15"/>
@@ -2713,7 +2713,7 @@
         <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E18" s="1"/>
       <c r="K18" s="15"/>
@@ -2726,7 +2726,7 @@
         <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E19" s="1"/>
       <c r="K19" s="15"/>
@@ -2736,10 +2736,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E20" s="1"/>
       <c r="K20" s="15"/>
@@ -2752,7 +2752,7 @@
         <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E21" s="1"/>
       <c r="K21" s="15"/>
@@ -2849,7 +2849,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7WMZ1mDUyvhL4UpKWt0nfcgkaCP0BpTdJaHaP4ZqioaIBj5Otagyz61Gxt0x4SOLv8AaGVTwJsZOUhjfi81XSw==" saltValue="yvb7SbXdXcRytveSJfy99Q==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jR8GCch154aOKGvz+bU3PSrpfN5AU1y4PMuc0z5ASCVBpPdGGKzAPFkdoJgP3tP33uksEet9JjLtv3ZVTTgGQg==" saltValue="Opzwxqah70w5eqZhGs+C8g==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/ckanext/lhm/schemas/template_master.xlsx
+++ b/ckanext/lhm/schemas/template_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\home\mb\p2\ckanext-lhm\ckanext\lhm\schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE41826-D22D-477B-9CB4-42AA63F6D747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04323879-7628-4EC9-9E0A-80199A761134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Wertelisten" sheetId="16" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Metadaten!$A$1:$K$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Metadaten!$A$1:$K$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="267">
   <si>
     <t>nein</t>
   </si>
@@ -774,6 +774,96 @@
   </si>
   <si>
     <t>ArcGIS Feature Service</t>
+  </si>
+  <si>
+    <t>Datenherkunft</t>
+  </si>
+  <si>
+    <t>Hinweise zur Datenerhebung</t>
+  </si>
+  <si>
+    <t>Inhaltlicher Stand der Daten</t>
+  </si>
+  <si>
+    <t>LHM-intern - GeoServicePlattform *</t>
+  </si>
+  <si>
+    <t>LHM-intern - GeoServicePlattform Gruppen</t>
+  </si>
+  <si>
+    <t>PLAN-DB</t>
+  </si>
+  <si>
+    <t>PLAN_MD_update-zyklus</t>
+  </si>
+  <si>
+    <t>quartalsweise</t>
+  </si>
+  <si>
+    <t>Jährlich</t>
+  </si>
+  <si>
+    <t>zweijährlich</t>
+  </si>
+  <si>
+    <t>PLAN_MD_schema</t>
+  </si>
+  <si>
+    <t>BAU</t>
+  </si>
+  <si>
+    <t>BPLAN</t>
+  </si>
+  <si>
+    <t>DENK</t>
+  </si>
+  <si>
+    <t>ENP</t>
+  </si>
+  <si>
+    <t>EWO</t>
+  </si>
+  <si>
+    <t>FIS</t>
+  </si>
+  <si>
+    <t>FNP</t>
+  </si>
+  <si>
+    <t>GEB</t>
+  </si>
+  <si>
+    <t>GEN</t>
+  </si>
+  <si>
+    <t>GRENZ</t>
+  </si>
+  <si>
+    <t>GRUEN</t>
+  </si>
+  <si>
+    <t>HAII_PRIO</t>
+  </si>
+  <si>
+    <t>INNENSTADT</t>
+  </si>
+  <si>
+    <t>LBK</t>
+  </si>
+  <si>
+    <t>REG</t>
+  </si>
+  <si>
+    <t>SIED</t>
+  </si>
+  <si>
+    <t>STAPL</t>
+  </si>
+  <si>
+    <t>UNB</t>
+  </si>
+  <si>
+    <t>ZEN</t>
   </si>
 </sst>
 </file>
@@ -1375,7 +1465,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{860E5F97-3212-47C5-A469-BCE2C1CB3CAC}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="48.5" style="14" customWidth="1"/>
@@ -1603,10 +1693,10 @@
       <c r="K13" s="17"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="20"/>
+      <c r="A14" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B14" s="22"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
@@ -1618,10 +1708,10 @@
       <c r="K14" s="17"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="B15" s="20"/>
+      <c r="A15" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B15" s="22"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
@@ -1633,10 +1723,10 @@
       <c r="K15" s="17"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="20"/>
+      <c r="A16" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B16" s="22"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
@@ -1647,11 +1737,11 @@
       <c r="J16" s="12"/>
       <c r="K16" s="17"/>
     </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="B17" s="22"/>
+    <row r="17" spans="1:11">
+      <c r="A17" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="20"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
@@ -1662,11 +1752,11 @@
       <c r="J17" s="12"/>
       <c r="K17" s="17"/>
     </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B18" s="22"/>
+    <row r="18" spans="1:11">
+      <c r="A18" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B18" s="20"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
@@ -1677,11 +1767,11 @@
       <c r="J18" s="12"/>
       <c r="K18" s="17"/>
     </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="B19" s="22"/>
+    <row r="19" spans="1:11">
+      <c r="A19" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="20"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
       <c r="E19" s="12"/>
@@ -1692,9 +1782,9 @@
       <c r="J19" s="12"/>
       <c r="K19" s="17"/>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:11">
       <c r="A20" s="16" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="12"/>
@@ -1707,9 +1797,9 @@
       <c r="J20" s="12"/>
       <c r="K20" s="17"/>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:11">
       <c r="A21" s="16" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="12"/>
@@ -1722,69 +1812,37 @@
       <c r="J21" s="12"/>
       <c r="K21" s="17"/>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:11">
       <c r="A22" s="16" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
       <c r="K22" s="17"/>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:11">
       <c r="A23" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B23" s="22"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
       <c r="K23" s="17"/>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:11">
       <c r="A24" s="16" t="s">
-        <v>154</v>
+        <v>240</v>
       </c>
       <c r="B24" s="22"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
       <c r="K24" s="17"/>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:11">
       <c r="A25" s="16" t="s">
-        <v>155</v>
+        <v>241</v>
       </c>
       <c r="B25" s="22"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
       <c r="K25" s="17"/>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:11">
       <c r="A26" s="16" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B26" s="22"/>
       <c r="C26" s="12"/>
@@ -1797,39 +1855,39 @@
       <c r="J26" s="12"/>
       <c r="K26" s="17"/>
     </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B27" s="20"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" s="18" t="s">
-        <v>228</v>
+    <row r="27" spans="1:11">
+      <c r="A27" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="17"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="16" t="s">
+        <v>154</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="12"/>
@@ -1840,14 +1898,13 @@
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="B30" s="26"/>
+      <c r="K29" s="17"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B30" s="22"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
       <c r="E30" s="12"/>
@@ -1856,14 +1913,13 @@
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="27"/>
+      <c r="K30" s="17"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B31" s="22"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
       <c r="E31" s="12"/>
@@ -1872,87 +1928,134 @@
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="B32" s="27"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" s="20"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="B33" s="27" t="s">
-        <v>234</v>
-      </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
+      <c r="A33" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="20"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="B34" s="22"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="14" t="s">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B35" s="26"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="27"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B37" s="27"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
-      <c r="A38" s="30" t="s">
+    <row r="43" spans="1:12">
+      <c r="A43" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
-    </row>
-    <row r="39" spans="1:12">
-      <c r="A39" s="31"/>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-    </row>
-    <row r="40" spans="1:12">
-      <c r="A40" s="31"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-    </row>
-    <row r="41" spans="1:12">
-      <c r="A41" s="31"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-    </row>
-    <row r="42" spans="1:12">
-      <c r="A42" s="31"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="A43" s="31"/>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
       <c r="D43" s="31"/>
@@ -1975,45 +2078,79 @@
       <c r="C46" s="31"/>
       <c r="D46" s="31"/>
     </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="31"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" s="31"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="31"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="31"/>
+      <c r="B50" s="31"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="31"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A38:D46"/>
+    <mergeCell ref="A43:D51"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations xWindow="1350" yWindow="369" count="33">
+  <dataValidations xWindow="1350" yWindow="369" count="37">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Thema | NAME_DER_TABELLE." prompt="Der Titel beteht aus dem Thema (für Geodatenpool: ehemals Datenbestand) und dem Namen der Tabelle in der Datenbank." sqref="B2" xr:uid="{7CC76290-C397-4A0D-82F8-39029843BD91}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Klare und prägnante Beschreibung des Datensatzes, damit auch Laien den Inhalt verstehen und einschätzen können. Dazu können neben dem konkreten Inhalt z.B. die räumliche Abdeckung, Vollständigkeit, Urheberschaft und Aktualität gehören." sqref="B4" xr:uid="{F0D16E7B-F9FC-4508-96CB-4EA176A334B4}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Schlagworte sind i.d.R. Substantive zur inhaltlichen Beschreibung des Datensatzes. Es können mehrere Schlagworte vergeben werden." sqref="B5" xr:uid="{623C178E-EC83-43E9-958F-0440F931AA20}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Hier können ergänzende Informationen zur Lagegenauigkeit ergänzt werden, beispielsweise ein geeigneter Maßstab (z.B. 1:500), die Größe eines Pixels (z.B. 20cm) oder die Spanne der Abweichung bei der Lage (z.B. +/- 10m)." sqref="B9" xr:uid="{970220F6-FBF5-4CF5-BE13-F3DFE3BCB688}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Angabe des fachlich zuständigen Referats und der ersten, das Referat untergliedernden Organisationseinheit (z.B. Amt, Hauptabteilung, Geschäftsbereich)" sqref="B10" xr:uid="{09939F82-660A-44C0-8D41-AB87CD53810A}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Angabe der Organisationseinheit, die fachliche und organisatorische Kenntnis zum Datensatz hat" sqref="B11" xr:uid="{BE1FC14A-141B-48FB-BA17-F9E0540C34BB}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Zusätzliche Hinweise zur Nutzung können unter 'Hinweise' mit Stichwort und Erklärung eingefügt werden. Diese müssen auch für Laien verständlich sein. Hinweise können z.B. zu vertraglichen Bedingungen oder Besonderheiten des Datensatzes erfolgen._x000a__x000a_" sqref="B28" xr:uid="{41DA2449-4EB8-42B0-8B24-A586BE48D043}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Um externe Datenurheber handelt es sich, wenn die Daten nicht von der Landeshautpststadt München stammen (z.B. LDBV)." sqref="B13" xr:uid="{6FD9F116-7FAD-43B8-974A-91F50455A327}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Zugriffsuser" prompt="Ist der Zugriff auf bestimmte Zugriffsuser zu beschränken, sind hier die entsprechenden User anzugeben (Komma als Trennzeichen)" sqref="B18" xr:uid="{5BFD9ECE-5759-4364-8421-D1A1E51E2D29}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Eingeschränkter Zugriff" prompt="Ist der Zugriff auf bestimmte Gruppen/Organisationseinheiten im GeoInfoWeb zu beschränken, sind hier die entsprechenden Gruppen/Organisationseinheiten anzugeben (Komma als Trennzeichen)" sqref="B20" xr:uid="{E9F37E1E-B0FC-4703-9265-EF66076FF35D}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Zusätzliche Hinweise zur Nutzung können unter 'Hinweise' mit Stichwort und Erklärung eingefügt werden. Diese müssen auch für Laien verständlich sein. Hinweise können z.B. zu vertraglichen Bedingungen oder Besonderheiten des Datensatzes erfolgen._x000a__x000a_" sqref="B33" xr:uid="{41DA2449-4EB8-42B0-8B24-A586BE48D043}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Um externe Datenurheber handelt es sich, wenn die Daten nicht von der Landeshautpststadt München stammen (z.B. LDBV)." sqref="B13 B16" xr:uid="{6FD9F116-7FAD-43B8-974A-91F50455A327}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Zugriffsuser" prompt="Ist der Zugriff auf bestimmte Zugriffsuser zu beschränken, sind hier die entsprechenden User anzugeben (Komma als Trennzeichen)" sqref="B21" xr:uid="{5BFD9ECE-5759-4364-8421-D1A1E51E2D29}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Eingeschränkter Zugriff" prompt="Ist der Zugriff auf bestimmte Gruppen/Organisationseinheiten im GeoInfoWeb zu beschränken, sind hier die entsprechenden Gruppen/Organisationseinheiten anzugeben (Komma als Trennzeichen)" sqref="B23" xr:uid="{E9F37E1E-B0FC-4703-9265-EF66076FF35D}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name des Datenbankschemas" prompt="(z.B. BAU, PLAN, RKU im Geodatenpool)" sqref="B3" xr:uid="{C8676A5A-F5FC-4B9E-975C-CB6983604CAE}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Die Auswahl legt fest, ob Daten für Backend und Präsentation, externe Auftragnehmer (mit Vertrag) oder sonstige Dritte (mit Bedingungen) nutzbar sind. Einschränkungen können bestimmte Inhalte oder Attribute betreffen. Ausführliche Hinweise zum Feld s.u." sqref="B22" xr:uid="{3865BC3F-EC1E-43CB-A54F-659A2F5AB813}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Mit dem Updatezyklus kann angegeben werden, ob und wie regelmäßig die Daten in der Datenbank aktualisiert werden." sqref="B14" xr:uid="{BD09D3BE-047F-41E0-9A7E-A7A85A3369A6}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Die Bewertung der Archivwürdigkeit erfolgt durch das Stadtarchiv" sqref="B15" xr:uid="{8A048881-B550-43EE-805E-C2EA2A69558E}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Form in der die Daten im Internet bereitgestellt werden dürfen. &quot;Als Backend-Daten (ohne Präsentation&quot; meint die Nutzung z.B. für Online-Formulare. &quot;Für Präsentationen (inkl. Backend)&quot; erweitert die Freigabe (GeoPortal, muenchen.de, kartog. Darstellungen)" sqref="B22" xr:uid="{A41F8A76-9455-4B99-9519-9F93DB75E5DB}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Sind nur ausgewählte Attribute oder Inhalte des Datensatzes zur Open-Data-Nutzung freigegeben, können die Attributnamen bzw. Inhalte hier definiert werden, z.B. OBJECTID, HAUSNR, GEMEINDE." sqref="B26" xr:uid="{EB2A74B3-0AE7-4C1D-82B1-F9DD4943055D}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Die Auswahl legt fest, ob Daten für Backend und Präsentation, externe Auftragnehmer (mit Vertrag) oder sonstige Dritte (mit Bedingungen) nutzbar sind. Einschränkungen können bestimmte Inhalte oder Attribute betreffen. Ausführliche Hinweise zum Feld s.u." sqref="B27" xr:uid="{3865BC3F-EC1E-43CB-A54F-659A2F5AB813}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Mit dem Updatezyklus kann angegeben werden, ob und wie regelmäßig die Daten in der Datenbank aktualisiert werden." sqref="B17" xr:uid="{BD09D3BE-047F-41E0-9A7E-A7A85A3369A6}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Die Bewertung der Archivwürdigkeit erfolgt durch das Stadtarchiv" sqref="B18" xr:uid="{8A048881-B550-43EE-805E-C2EA2A69558E}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Form in der die Daten im Internet bereitgestellt werden dürfen. &quot;Als Backend-Daten (ohne Präsentation&quot; meint die Nutzung z.B. für Online-Formulare. &quot;Für Präsentationen (inkl. Backend)&quot; erweitert die Freigabe (GeoPortal, muenchen.de, kartog. Darstellungen)" sqref="B27" xr:uid="{A41F8A76-9455-4B99-9519-9F93DB75E5DB}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Sind nur ausgewählte Attribute oder Inhalte des Datensatzes zur Open-Data-Nutzung freigegeben, können die Attributnamen bzw. Inhalte hier definiert werden, z.B. OBJECTID, HAUSNR, GEMEINDE." sqref="B31" xr:uid="{EB2A74B3-0AE7-4C1D-82B1-F9DD4943055D}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Mit der Lagegenauigkeit wird angegeben, auf welcher Basis Daten erhoben bzw. erfasst wurden und welche räumliche Genauigkeit damit einhergeht." sqref="B8" xr:uid="{04C3394C-C73C-4666-8D58-5B4DCD9F8885}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Themen sind eine Möglichkeit zur inhaltlich-thematischen Kategorisierung von Datensätzen. Es ist mindestens ein passendes Thema auszuwählen." sqref="B6" xr:uid="{C0289FFA-04C1-439D-8D1E-80EC7B4FB682}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Information über den direkten (lesenden) Zugriff auf die Daten auf der Datenbank durch Mitarbeitende und/oder über Dienste innerhalb der LHM. Teilweise ist der Zugriff für bestimmte Benutzergruppen (auch: Zugriffsuser von Fachverfahren) einzuschränken." sqref="B17" xr:uid="{768E5D3D-B1E5-4EAB-8C95-0284B7839969}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Der GeoInfoWeb-Zugriff, und damit die Sichtbarkeit der Daten, kann auf Nutzergruppen beschränkt werden. Standard ist stadtweiter Zugriff. 'Ausgenommen Bezirksausschüsse' bedeutet, dass alle außer den Bezirksausschüssen Zugriff haben." sqref="B19" xr:uid="{F968230D-8F99-4488-8588-8668AB2F2BD8}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Falls HVD im Datensatz enthalten sind, ist hier die Kategorie der HVD gemäß Verordnung auszuwählen." sqref="B25" xr:uid="{249E43EF-C3D0-46E7-91CC-0080ADBBA82B}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Infos zu Zugriffsrechten und Bereitstellung für Externe, d.h. Personen und Organisationen außerhalb der LHM. Bei externer Datennutzung gelten Nutzungsbedingungen. Einschränkungen sind im Feld 'Nutzungsoptionen bei Einschränkungen' zu definieren." sqref="B21" xr:uid="{F0426A99-0C4F-4166-AA6B-F1C947114BF4}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Mit Open Data sind Daten gemeint, die frei verfügbar gemacht und frei genutzt werden können." sqref="B23" xr:uid="{3F17D9AC-8A69-4E15-A107-24F4D0EC6C8C}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Begründung der Archivwürdigkeit" sqref="B16" xr:uid="{B5C9230F-0AAA-418B-B401-1C64BB7D5AB9}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Letzte Aktualisierung der Datentabelle in der Datenquelle." sqref="B31" xr:uid="{90F3683F-43B8-4EDC-9A81-A6152C8C4181}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Einträge im Katalog können auf verschiedene Weisen gruppiert werden. Jeder Eintrag muss einer Hauptkategorie zugeordnet werden, die die Art der Informationsressource angibt und damit die benötigten Metadaten bestimmt." sqref="B30" xr:uid="{5C272E7B-EE52-42D1-BDE6-28A59E5A56DE}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Information über den direkten (lesenden) Zugriff auf die Daten auf der Datenbank durch Mitarbeitende und/oder über Dienste innerhalb der LHM. Teilweise ist der Zugriff für bestimmte Benutzergruppen (auch: Zugriffsuser von Fachverfahren) einzuschränken." sqref="B20" xr:uid="{768E5D3D-B1E5-4EAB-8C95-0284B7839969}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Der GeoInfoWeb-Zugriff, und damit die Sichtbarkeit der Daten, kann auf Nutzergruppen beschränkt werden. Standard ist stadtweiter Zugriff. 'Ausgenommen Bezirksausschüsse' bedeutet, dass alle außer den Bezirksausschüssen Zugriff haben." sqref="B22" xr:uid="{F968230D-8F99-4488-8588-8668AB2F2BD8}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Falls HVD im Datensatz enthalten sind, ist hier die Kategorie der HVD gemäß Verordnung auszuwählen." sqref="B30" xr:uid="{249E43EF-C3D0-46E7-91CC-0080ADBBA82B}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Infos zu Zugriffsrechten und Bereitstellung für Externe, d.h. Personen und Organisationen außerhalb der LHM. Bei externer Datennutzung gelten Nutzungsbedingungen. Einschränkungen sind im Feld 'Nutzungsoptionen bei Einschränkungen' zu definieren." sqref="B26" xr:uid="{F0426A99-0C4F-4166-AA6B-F1C947114BF4}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Mit Open Data sind Daten gemeint, die frei verfügbar gemacht und frei genutzt werden können." sqref="B28" xr:uid="{3F17D9AC-8A69-4E15-A107-24F4D0EC6C8C}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Begründung der Archivwürdigkeit" sqref="B19" xr:uid="{B5C9230F-0AAA-418B-B401-1C64BB7D5AB9}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Letzte Aktualisierung der Datentabelle in der Datenquelle." sqref="B36" xr:uid="{90F3683F-43B8-4EDC-9A81-A6152C8C4181}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Einträge im Katalog können auf verschiedene Weisen gruppiert werden. Jeder Eintrag muss einer Hauptkategorie zugeordnet werden, die die Art der Informationsressource angibt und damit die benötigten Metadaten bestimmt." sqref="B35" xr:uid="{5C272E7B-EE52-42D1-BDE6-28A59E5A56DE}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Angabe des in der Tabelle enthaltenen Objekttyps" sqref="B7" xr:uid="{B4696CB2-B201-4617-B305-E5BD75EB61D4}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Angabe der Team-E-Mailadresse des Datenverantwortlichen" sqref="B12" xr:uid="{BE4AF42B-6330-4B78-96B6-38C329A34190}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Mit High Value Datasets sind Daten gemeint, die in unter die DVO-HVD fallen. HVD-Daten sind per Definition immer auch Open Data." sqref="B24" xr:uid="{AC7FDAAF-072D-4534-A3F9-2DE40D62DD74}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Einstellung zur Sichtbarkeit des eingetragenen Metadatensatzes. Öffentlich: Sichtbarkeit für alle Personen in der LHM (Standard). Privat: Sichtbarkeit nur für Mitglieder der zuständigen Organisation." sqref="B29" xr:uid="{76CBF2A2-3862-46A6-9110-A30535030C72}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Zusätzliche Hinweise zur Nutzung können unter 'Hinweise' mit Stichwort und Erklärung eingefügt werden. Diese müssen auch für Laien verständlich sein. Hinweise können z.B. zu vertraglichen Bedingungen oder Besonderheiten des Datensatzes erfolgen." sqref="B27" xr:uid="{4DD816CA-8275-41A8-B3C6-1162E00F43EE}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Die Datenquelle bezeichnet das System aus dem die Daten bezogen werden können, bspw. Geodatenpool." sqref="B32" xr:uid="{4BB7D51D-AB96-4002-8175-8BC4894AA0F9}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Version des Formats dieser Excel-Vorlage" sqref="B33" xr:uid="{DE5565F3-E0DE-421D-8CEB-430905832D21}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Mit High Value Datasets sind Daten gemeint, die in unter die DVO-HVD fallen. HVD-Daten sind per Definition immer auch Open Data." sqref="B29" xr:uid="{AC7FDAAF-072D-4534-A3F9-2DE40D62DD74}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Einstellung zur Sichtbarkeit des eingetragenen Metadatensatzes. Öffentlich: Sichtbarkeit für alle Personen in der LHM (Standard). Privat: Sichtbarkeit nur für Mitglieder der zuständigen Organisation." sqref="B34" xr:uid="{76CBF2A2-3862-46A6-9110-A30535030C72}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Zusätzliche Hinweise zur Nutzung können unter 'Hinweise' mit Stichwort und Erklärung eingefügt werden. Diese müssen auch für Laien verständlich sein. Hinweise können z.B. zu vertraglichen Bedingungen oder Besonderheiten des Datensatzes erfolgen." sqref="B32" xr:uid="{4DD816CA-8275-41A8-B3C6-1162E00F43EE}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Die Datenquelle bezeichnet das System aus dem die Daten bezogen werden können, bspw. Geodatenpool." sqref="B37" xr:uid="{4BB7D51D-AB96-4002-8175-8BC4894AA0F9}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Version des Formats dieser Excel-Vorlage" sqref="B38" xr:uid="{DE5565F3-E0DE-421D-8CEB-430905832D21}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Angabe über Herkunft der Daten, falls ein externer Datenurheber vorhanden ist." sqref="B14" xr:uid="{893E1363-EB8D-44CC-8DA3-7B73FBE71364}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Beschreibt den Vorgang des Geoprocessing von den Rohdaten bis zu den Fachdaten." sqref="B15" xr:uid="{ADF3A5C0-6EDA-457C-9197-256C14BF8AF4}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Legt fest ob die Daten auf der GeoServicePlattform abrufbar sind und synchronisiert werden." sqref="B24" xr:uid="{8FBB7983-3955-4A4B-B266-AF68B19178E6}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Eingeschränkter Zugriff" prompt="Ist der Zugriff auf bestimmte Gruppen/ Organisationseinheiten auf der GeoServicePlattform beschränkt, sind diese hier anzugeben (Komma als Trennzeichen)." sqref="B25" xr:uid="{2D5E2408-E8A8-4925-87FB-78E1DE201641}"/>
   </dataValidations>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="64" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -2137,7 +2274,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D073E50-F226-4B6A-BC2C-397D6C68AFA7}">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:X36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="22.3984375" bestFit="1" customWidth="1"/>
@@ -2161,9 +2298,11 @@
     <col min="20" max="20" width="23.796875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="27.3984375" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.8984375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1">
+    <row r="1" spans="1:24" s="1" customFormat="1">
       <c r="A1" s="5" t="s">
         <v>204</v>
       </c>
@@ -2230,8 +2369,14 @@
       <c r="V1" s="5" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2294,8 +2439,14 @@
       <c r="V2" s="2" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="W2" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2362,8 +2513,14 @@
       <c r="V3" s="2" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="4" spans="1:22">
+      <c r="W3" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -2418,8 +2575,17 @@
       <c r="U4" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="V4" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -2456,8 +2622,14 @@
       <c r="U5" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="W5" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -2494,8 +2666,14 @@
       <c r="U6" s="2" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="W6" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -2526,8 +2704,14 @@
       <c r="U7" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="W7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -2558,8 +2742,14 @@
       <c r="U8" s="2" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="W8" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -2579,8 +2769,14 @@
       <c r="U9" s="2" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="W9" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -2601,8 +2797,14 @@
       <c r="U10" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="W10" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2623,8 +2825,14 @@
       <c r="U11" s="2" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="W11" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -2639,8 +2847,11 @@
       <c r="U12" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="W12" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -2652,8 +2863,11 @@
       </c>
       <c r="E13" s="1"/>
       <c r="K13" s="15"/>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="W13" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -2665,8 +2879,11 @@
       </c>
       <c r="E14" s="1"/>
       <c r="K14" s="15"/>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="W14" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -2678,8 +2895,11 @@
       </c>
       <c r="E15" s="1"/>
       <c r="K15" s="15"/>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="W15" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -2691,8 +2911,11 @@
       </c>
       <c r="E16" s="1"/>
       <c r="K16" s="15"/>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="W16" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -2704,8 +2927,11 @@
       </c>
       <c r="E17" s="1"/>
       <c r="K17" s="15"/>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="W17" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -2717,8 +2943,11 @@
       </c>
       <c r="E18" s="1"/>
       <c r="K18" s="15"/>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="W18" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -2730,8 +2959,11 @@
       </c>
       <c r="E19" s="1"/>
       <c r="K19" s="15"/>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="W19" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -2743,8 +2975,11 @@
       </c>
       <c r="E20" s="1"/>
       <c r="K20" s="15"/>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="W20" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -2756,8 +2991,11 @@
       </c>
       <c r="E21" s="1"/>
       <c r="K21" s="15"/>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="W21" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -2766,7 +3004,7 @@
       </c>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:23">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
@@ -2775,55 +3013,55 @@
       </c>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:23">
       <c r="B24" s="2" t="s">
         <v>44</v>
       </c>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:23">
       <c r="B25" s="2" t="s">
         <v>45</v>
       </c>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:23">
       <c r="B26" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:23">
       <c r="B27" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:23">
       <c r="B28" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:23">
       <c r="B29" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:23">
       <c r="B30" s="2" t="s">
         <v>50</v>
       </c>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:23">
       <c r="B31" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:23">
       <c r="B32" s="2" t="s">
         <v>52</v>
       </c>
@@ -2849,7 +3087,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jR8GCch154aOKGvz+bU3PSrpfN5AU1y4PMuc0z5ASCVBpPdGGKzAPFkdoJgP3tP33uksEet9JjLtv3ZVTTgGQg==" saltValue="Opzwxqah70w5eqZhGs+C8g==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PH4zrp7eXCCYTe30bZgWa4oN323isiTnw119OHfSlXEE4aKSPiWff8viQcR9grAl1yuVHM8VUpNSbGDq2VjIJA==" saltValue="JZVoZuV7oNQazjtxqkPBpg==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/ckanext/lhm/schemas/template_master.xlsx
+++ b/ckanext/lhm/schemas/template_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\home\mb\p2\ckanext-lhm\ckanext\lhm\schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04323879-7628-4EC9-9E0A-80199A761134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E13F00-D7CC-45C3-806A-7A8B48DF3D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
   </bookViews>
@@ -797,15 +797,9 @@
     <t>PLAN_MD_update-zyklus</t>
   </si>
   <si>
-    <t>quartalsweise</t>
-  </si>
-  <si>
     <t>Jährlich</t>
   </si>
   <si>
-    <t>zweijährlich</t>
-  </si>
-  <si>
     <t>PLAN_MD_schema</t>
   </si>
   <si>
@@ -864,6 +858,12 @@
   </si>
   <si>
     <t>ZEN</t>
+  </si>
+  <si>
+    <t>Quartalsweise</t>
+  </si>
+  <si>
+    <t>Zweijährlich</t>
   </si>
 </sst>
 </file>
@@ -2370,7 +2370,7 @@
         <v>229</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="X1" s="5" t="s">
         <v>243</v>
@@ -2440,7 +2440,7 @@
         <v>230</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>104</v>
@@ -2514,7 +2514,7 @@
         <v>231</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="X3" s="2" t="s">
         <v>143</v>
@@ -2579,7 +2579,7 @@
         <v>242</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>144</v>
@@ -2623,7 +2623,7 @@
         <v>90</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="X5" s="2" t="s">
         <v>145</v>
@@ -2667,7 +2667,7 @@
         <v>195</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>146</v>
@@ -2705,7 +2705,7 @@
         <v>194</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>105</v>
@@ -2743,10 +2743,10 @@
         <v>196</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -2770,10 +2770,10 @@
         <v>198</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -2798,10 +2798,10 @@
         <v>197</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -2826,7 +2826,7 @@
         <v>199</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>106</v>
@@ -2848,7 +2848,7 @@
         <v>200</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -2864,7 +2864,7 @@
       <c r="E13" s="1"/>
       <c r="K13" s="15"/>
       <c r="W13" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -2880,7 +2880,7 @@
       <c r="E14" s="1"/>
       <c r="K14" s="15"/>
       <c r="W14" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -2896,7 +2896,7 @@
       <c r="E15" s="1"/>
       <c r="K15" s="15"/>
       <c r="W15" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -2912,7 +2912,7 @@
       <c r="E16" s="1"/>
       <c r="K16" s="15"/>
       <c r="W16" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -2928,7 +2928,7 @@
       <c r="E17" s="1"/>
       <c r="K17" s="15"/>
       <c r="W17" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -2960,7 +2960,7 @@
       <c r="E19" s="1"/>
       <c r="K19" s="15"/>
       <c r="W19" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -2976,7 +2976,7 @@
       <c r="E20" s="1"/>
       <c r="K20" s="15"/>
       <c r="W20" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -2992,7 +2992,7 @@
       <c r="E21" s="1"/>
       <c r="K21" s="15"/>
       <c r="W21" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -3087,7 +3087,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="PH4zrp7eXCCYTe30bZgWa4oN323isiTnw119OHfSlXEE4aKSPiWff8viQcR9grAl1yuVHM8VUpNSbGDq2VjIJA==" saltValue="JZVoZuV7oNQazjtxqkPBpg==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="XIhFgadR1bmyL3SPoHS41+3tUZqsLtqcbU4VzMIUMew96ptGIJKwvbDRU4h465yFQ0fDb5h+uNZvr6erUHABag==" saltValue="nyUB6A+Q9PWi/8oZYGFrAA==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/ckanext/lhm/schemas/template_master.xlsx
+++ b/ckanext/lhm/schemas/template_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\home\mb\p2\ckanext-lhm\ckanext\lhm\schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E13F00-D7CC-45C3-806A-7A8B48DF3D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697216BC-2819-4E06-9D1E-C0BAEE673231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="269">
   <si>
     <t>nein</t>
   </si>
@@ -767,9 +767,6 @@
     <t>Bedeutung</t>
   </si>
   <si>
-    <t>1.3.2.</t>
-  </si>
-  <si>
     <t>ArcGIS Map Service</t>
   </si>
   <si>
@@ -864,6 +861,15 @@
   </si>
   <si>
     <t>Zweijährlich</t>
+  </si>
+  <si>
+    <t>WMTS-KVP</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>1.3.3.</t>
   </si>
 </sst>
 </file>
@@ -1694,7 +1700,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="12"/>
@@ -1709,7 +1715,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="12"/>
@@ -1724,7 +1730,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B16" s="22"/>
       <c r="C16" s="12"/>
@@ -1828,14 +1834,14 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B24" s="22"/>
       <c r="K24" s="17"/>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B25" s="22"/>
       <c r="K25" s="17"/>
@@ -2029,7 +2035,7 @@
         <v>202</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>234</v>
+        <v>268</v>
       </c>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
@@ -2370,10 +2376,10 @@
         <v>229</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:24">
@@ -2440,7 +2446,7 @@
         <v>230</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>104</v>
@@ -2514,7 +2520,7 @@
         <v>231</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="X3" s="2" t="s">
         <v>143</v>
@@ -2576,10 +2582,10 @@
         <v>91</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>144</v>
@@ -2623,7 +2629,7 @@
         <v>90</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X5" s="2" t="s">
         <v>145</v>
@@ -2667,7 +2673,7 @@
         <v>195</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>146</v>
@@ -2699,13 +2705,13 @@
         <v>199</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>99</v>
+        <v>266</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>194</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>105</v>
@@ -2737,16 +2743,16 @@
         <v>93</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>196</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -2764,16 +2770,16 @@
         <v>119</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>235</v>
+        <v>100</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>198</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -2792,16 +2798,16 @@
       </c>
       <c r="K10" s="15"/>
       <c r="R10" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>197</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -2820,13 +2826,13 @@
       </c>
       <c r="K11" s="15"/>
       <c r="R11" s="2" t="s">
-        <v>86</v>
+        <v>235</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>199</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>106</v>
@@ -2844,11 +2850,14 @@
       </c>
       <c r="E12" s="1"/>
       <c r="K12" s="15"/>
+      <c r="R12" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="U12" s="2" t="s">
         <v>200</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -2863,8 +2872,11 @@
       </c>
       <c r="E13" s="1"/>
       <c r="K13" s="15"/>
+      <c r="R13" s="2" t="s">
+        <v>267</v>
+      </c>
       <c r="W13" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -2880,7 +2892,7 @@
       <c r="E14" s="1"/>
       <c r="K14" s="15"/>
       <c r="W14" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -2896,7 +2908,7 @@
       <c r="E15" s="1"/>
       <c r="K15" s="15"/>
       <c r="W15" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -2912,7 +2924,7 @@
       <c r="E16" s="1"/>
       <c r="K16" s="15"/>
       <c r="W16" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -2928,7 +2940,7 @@
       <c r="E17" s="1"/>
       <c r="K17" s="15"/>
       <c r="W17" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -2960,7 +2972,7 @@
       <c r="E19" s="1"/>
       <c r="K19" s="15"/>
       <c r="W19" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -2976,7 +2988,7 @@
       <c r="E20" s="1"/>
       <c r="K20" s="15"/>
       <c r="W20" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -2992,7 +3004,7 @@
       <c r="E21" s="1"/>
       <c r="K21" s="15"/>
       <c r="W21" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -3087,7 +3099,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="XIhFgadR1bmyL3SPoHS41+3tUZqsLtqcbU4VzMIUMew96ptGIJKwvbDRU4h465yFQ0fDb5h+uNZvr6erUHABag==" saltValue="nyUB6A+Q9PWi/8oZYGFrAA==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ilEvpGmLo6a2O3ZAU+i9yQGGscrus6aYietO82VMOaIJdasi+nuCz4K4VGwvF5eoMx2reLQ9A/c/BCnrtsR9rw==" saltValue="4P2QQwj56WNptjDpbIU8kA==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/ckanext/lhm/schemas/template_master.xlsx
+++ b/ckanext/lhm/schemas/template_master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\home\mb\p2\ckanext-lhm\ckanext\lhm\schemas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\home\mb\dev\ckanext-lhm\ckanext\lhm\schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697216BC-2819-4E06-9D1E-C0BAEE673231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9096338C-E074-4D18-B04A-EF2ED94BFE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
+    <workbookView xWindow="684" yWindow="240" windowWidth="23016" windowHeight="12108" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadaten" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Wertelisten" sheetId="16" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Metadaten!$A$1:$K$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Metadaten!$A$1:$K$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="270">
   <si>
     <t>nein</t>
   </si>
@@ -259,9 +259,6 @@
   </si>
   <si>
     <t>Wert 10</t>
-  </si>
-  <si>
-    <t>Organisation *</t>
   </si>
   <si>
     <t>Externe Datenurheber *</t>
@@ -869,7 +866,13 @@
     <t>Link</t>
   </si>
   <si>
-    <t>1.3.3.</t>
+    <t>Abteilung *</t>
+  </si>
+  <si>
+    <t>1.3.6.</t>
+  </si>
+  <si>
+    <t>Metadatenschema *</t>
   </si>
 </sst>
 </file>
@@ -1471,7 +1474,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{860E5F97-3212-47C5-A469-BCE2C1CB3CAC}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="48.5" style="14" customWidth="1"/>
@@ -1520,7 +1523,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="12"/>
@@ -1535,7 +1538,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="12"/>
@@ -1550,7 +1553,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B4" s="21"/>
       <c r="C4" s="12"/>
@@ -1565,7 +1568,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="24"/>
@@ -1580,7 +1583,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="22"/>
@@ -1595,7 +1598,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="12"/>
@@ -1610,7 +1613,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="12"/>
@@ -1640,7 +1643,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="16" t="s">
-        <v>71</v>
+        <v>267</v>
       </c>
       <c r="B10" s="22"/>
       <c r="C10" s="12"/>
@@ -1655,7 +1658,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="12"/>
@@ -1670,7 +1673,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="12"/>
@@ -1685,7 +1688,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B13" s="22"/>
       <c r="C13" s="12"/>
@@ -1700,7 +1703,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="12"/>
@@ -1715,7 +1718,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="12"/>
@@ -1730,7 +1733,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B16" s="22"/>
       <c r="C16" s="12"/>
@@ -1745,7 +1748,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="12"/>
@@ -1760,7 +1763,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="12"/>
@@ -1790,7 +1793,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="12"/>
@@ -1805,7 +1808,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="12"/>
@@ -1820,35 +1823,35 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B22" s="22"/>
       <c r="K22" s="17"/>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B23" s="22"/>
       <c r="K23" s="17"/>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B24" s="22"/>
       <c r="K24" s="17"/>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B25" s="22"/>
       <c r="K25" s="17"/>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B26" s="22"/>
       <c r="C26" s="12"/>
@@ -1863,7 +1866,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -1878,7 +1881,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="12"/>
@@ -1893,7 +1896,7 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="12"/>
@@ -1908,7 +1911,7 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B30" s="22"/>
       <c r="C30" s="12"/>
@@ -1923,7 +1926,7 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B31" s="22"/>
       <c r="C31" s="12"/>
@@ -1938,7 +1941,7 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="25"/>
@@ -1953,7 +1956,7 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="25"/>
@@ -1968,7 +1971,7 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="18" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B34" s="22"/>
       <c r="C34" s="12"/>
@@ -1984,7 +1987,7 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B35" s="26"/>
       <c r="C35" s="12"/>
@@ -2000,7 +2003,7 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B36" s="27"/>
       <c r="C36" s="12"/>
@@ -2016,7 +2019,7 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B37" s="27"/>
       <c r="C37" s="12"/>
@@ -2032,11 +2035,9 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="B38" s="27" t="s">
-        <v>268</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="B38" s="27"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
       <c r="E38" s="12"/>
@@ -2048,26 +2049,38 @@
       <c r="K38" s="12"/>
       <c r="L38" s="12"/>
     </row>
-    <row r="40" spans="1:12">
-      <c r="A40" s="14" t="s">
-        <v>75</v>
-      </c>
+    <row r="39" spans="1:12">
+      <c r="A39" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="12"/>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="A43" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="14" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="31"/>
+      <c r="A44" s="30" t="s">
+        <v>192</v>
+      </c>
       <c r="B44" s="31"/>
       <c r="C44" s="31"/>
       <c r="D44" s="31"/>
@@ -2114,12 +2127,18 @@
       <c r="C51" s="31"/>
       <c r="D51" s="31"/>
     </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="31"/>
+      <c r="B52" s="31"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A43:D51"/>
+    <mergeCell ref="A44:D52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations xWindow="1350" yWindow="369" count="37">
+  <dataValidations xWindow="1350" yWindow="369" count="38">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Thema | NAME_DER_TABELLE." prompt="Der Titel beteht aus dem Thema (für Geodatenpool: ehemals Datenbestand) und dem Namen der Tabelle in der Datenbank." sqref="B2" xr:uid="{7CC76290-C397-4A0D-82F8-39029843BD91}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Klare und prägnante Beschreibung des Datensatzes, damit auch Laien den Inhalt verstehen und einschätzen können. Dazu können neben dem konkreten Inhalt z.B. die räumliche Abdeckung, Vollständigkeit, Urheberschaft und Aktualität gehören." sqref="B4" xr:uid="{F0D16E7B-F9FC-4508-96CB-4EA176A334B4}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Schlagworte sind i.d.R. Substantive zur inhaltlichen Beschreibung des Datensatzes. Es können mehrere Schlagworte vergeben werden." sqref="B5" xr:uid="{623C178E-EC83-43E9-958F-0440F931AA20}"/>
@@ -2151,12 +2170,13 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Mit High Value Datasets sind Daten gemeint, die in unter die DVO-HVD fallen. HVD-Daten sind per Definition immer auch Open Data." sqref="B29" xr:uid="{AC7FDAAF-072D-4534-A3F9-2DE40D62DD74}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Einstellung zur Sichtbarkeit des eingetragenen Metadatensatzes. Öffentlich: Sichtbarkeit für alle Personen in der LHM (Standard). Privat: Sichtbarkeit nur für Mitglieder der zuständigen Organisation." sqref="B34" xr:uid="{76CBF2A2-3862-46A6-9110-A30535030C72}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Zusätzliche Hinweise zur Nutzung können unter 'Hinweise' mit Stichwort und Erklärung eingefügt werden. Diese müssen auch für Laien verständlich sein. Hinweise können z.B. zu vertraglichen Bedingungen oder Besonderheiten des Datensatzes erfolgen." sqref="B32" xr:uid="{4DD816CA-8275-41A8-B3C6-1162E00F43EE}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Die Datenquelle bezeichnet das System aus dem die Daten bezogen werden können, bspw. Geodatenpool." sqref="B37" xr:uid="{4BB7D51D-AB96-4002-8175-8BC4894AA0F9}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Version des Formats dieser Excel-Vorlage" sqref="B38" xr:uid="{DE5565F3-E0DE-421D-8CEB-430905832D21}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Die Datenquelle bezeichnet das System aus dem die Daten bezogen werden können, z.B. Geodatenpool. An ihr hängen als CKAN owner_org außerdem die Bearbeitungsrechte des Metadatensatzes." sqref="B37" xr:uid="{4BB7D51D-AB96-4002-8175-8BC4894AA0F9}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Version des Formats dieser Excel-Vorlage" sqref="B39" xr:uid="{DE5565F3-E0DE-421D-8CEB-430905832D21}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Angabe über Herkunft der Daten, falls ein externer Datenurheber vorhanden ist." sqref="B14" xr:uid="{893E1363-EB8D-44CC-8DA3-7B73FBE71364}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Beschreibt den Vorgang des Geoprocessing von den Rohdaten bis zu den Fachdaten." sqref="B15" xr:uid="{ADF3A5C0-6EDA-457C-9197-256C14BF8AF4}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Legt fest ob die Daten auf der GeoServicePlattform abrufbar sind und synchronisiert werden." sqref="B24" xr:uid="{8FBB7983-3955-4A4B-B266-AF68B19178E6}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Eingeschränkter Zugriff" prompt="Ist der Zugriff auf bestimmte Gruppen/ Organisationseinheiten auf der GeoServicePlattform beschränkt, sind diese hier anzugeben (Komma als Trennzeichen)." sqref="B25" xr:uid="{2D5E2408-E8A8-4925-87FB-78E1DE201641}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Das Metadatenschema bezeichnet das Schema, in dem die Metadaten gespeichert werden." sqref="B38" xr:uid="{D70F36C4-1632-4D58-9CC9-03CC7D92E979}"/>
   </dataValidations>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="64" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -2180,22 +2200,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="28" t="s">
-        <v>184</v>
-      </c>
       <c r="C1" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D1" s="28" t="s">
         <v>57</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -2222,16 +2242,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>61</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2256,16 +2276,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="C1" s="28" t="s">
-        <v>88</v>
-      </c>
       <c r="D1" s="28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2310,76 +2330,76 @@
   <sheetData>
     <row r="1" spans="1:24" s="1" customFormat="1">
       <c r="A1" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="R1" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="O1" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q1" s="5" t="s">
+      <c r="S1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="R1" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>220</v>
-      </c>
       <c r="V1" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:24">
@@ -2390,66 +2410,66 @@
         <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="O2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="R2" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -2460,70 +2480,70 @@
         <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -2534,61 +2554,61 @@
         <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -2599,40 +2619,40 @@
         <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -2643,40 +2663,40 @@
         <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -2687,34 +2707,34 @@
         <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -2725,34 +2745,34 @@
         <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -2763,23 +2783,23 @@
         <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E9" s="1"/>
       <c r="G9" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -2790,24 +2810,24 @@
         <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E10" s="1"/>
       <c r="G10" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K10" s="15"/>
       <c r="R10" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -2818,24 +2838,24 @@
         <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E11" s="1"/>
       <c r="G11" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K11" s="15"/>
       <c r="R11" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -2846,18 +2866,18 @@
         <v>33</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E12" s="1"/>
       <c r="K12" s="15"/>
       <c r="R12" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -2868,15 +2888,15 @@
         <v>34</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E13" s="1"/>
       <c r="K13" s="15"/>
       <c r="R13" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -2887,12 +2907,12 @@
         <v>35</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E14" s="1"/>
       <c r="K14" s="15"/>
       <c r="W14" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -2903,12 +2923,12 @@
         <v>36</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E15" s="1"/>
       <c r="K15" s="15"/>
       <c r="W15" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -2919,12 +2939,12 @@
         <v>37</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E16" s="1"/>
       <c r="K16" s="15"/>
       <c r="W16" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -2935,12 +2955,12 @@
         <v>38</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E17" s="1"/>
       <c r="K17" s="15"/>
       <c r="W17" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -2951,12 +2971,12 @@
         <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E18" s="1"/>
       <c r="K18" s="15"/>
       <c r="W18" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:23">
@@ -2967,12 +2987,12 @@
         <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E19" s="1"/>
       <c r="K19" s="15"/>
       <c r="W19" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -2980,15 +3000,15 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E20" s="1"/>
       <c r="K20" s="15"/>
       <c r="W20" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -2999,12 +3019,12 @@
         <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E21" s="1"/>
       <c r="K21" s="15"/>
       <c r="W21" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="22" spans="1:23">

--- a/ckanext/lhm/schemas/template_master.xlsx
+++ b/ckanext/lhm/schemas/template_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\home\mb\dev\ckanext-lhm\ckanext\lhm\schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9096338C-E074-4D18-B04A-EF2ED94BFE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9038BD98-B645-45C2-8FF2-D7069FCC9C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="684" yWindow="240" windowWidth="23016" windowHeight="12108" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{EFAD0BDA-2C19-4F99-80E8-84599936D919}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadaten" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="271">
   <si>
     <t>nein</t>
   </si>
@@ -752,12 +752,6 @@
     <t>LHM_MD_datenquelle</t>
   </si>
   <si>
-    <t>Geodatenpool</t>
-  </si>
-  <si>
-    <t>Mobidam</t>
-  </si>
-  <si>
     <t>Attribut</t>
   </si>
   <si>
@@ -873,6 +867,15 @@
   </si>
   <si>
     <t>Metadatenschema *</t>
+  </si>
+  <si>
+    <t>GeoDatenPool</t>
+  </si>
+  <si>
+    <t>MobidaM</t>
+  </si>
+  <si>
+    <t>LHM_MD_metadatenschema</t>
   </si>
 </sst>
 </file>
@@ -1643,7 +1646,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="16" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B10" s="22"/>
       <c r="C10" s="12"/>
@@ -1703,7 +1706,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="16" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="12"/>
@@ -1718,7 +1721,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="12"/>
@@ -1733,7 +1736,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="16" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B16" s="22"/>
       <c r="C16" s="12"/>
@@ -1837,14 +1840,14 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B24" s="22"/>
       <c r="K24" s="17"/>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B25" s="22"/>
       <c r="K25" s="17"/>
@@ -2035,7 +2038,7 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B38" s="27"/>
       <c r="C38" s="12"/>
@@ -2054,7 +2057,7 @@
         <v>201</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
@@ -2245,13 +2248,13 @@
         <v>84</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>61</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2300,7 +2303,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D073E50-F226-4B6A-BC2C-397D6C68AFA7}">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:X36"/>
+  <dimension ref="A1:Y36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="22.3984375" bestFit="1" customWidth="1"/>
@@ -2326,9 +2329,10 @@
     <col min="22" max="22" width="18.8984375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="16.8984375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="21.796875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1">
+    <row r="1" spans="1:25" s="1" customFormat="1">
       <c r="A1" s="5" t="s">
         <v>203</v>
       </c>
@@ -2396,13 +2400,16 @@
         <v>228</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24">
+        <v>239</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2463,16 +2470,19 @@
         <v>92</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="3" spans="1:24">
+      <c r="Y2" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2537,16 +2547,19 @@
         <v>91</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="X3" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="4" spans="1:24">
+      <c r="Y3" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -2602,16 +2615,19 @@
         <v>90</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="5" spans="1:24">
+      <c r="Y4" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -2649,13 +2665,13 @@
         <v>89</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="X5" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -2693,13 +2709,13 @@
         <v>194</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:25">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -2725,19 +2741,19 @@
         <v>198</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>193</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -2769,13 +2785,13 @@
         <v>195</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -2796,13 +2812,13 @@
         <v>197</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -2818,19 +2834,19 @@
       </c>
       <c r="K10" s="15"/>
       <c r="R10" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>196</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2846,19 +2862,19 @@
       </c>
       <c r="K11" s="15"/>
       <c r="R11" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>198</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -2877,10 +2893,10 @@
         <v>199</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -2893,13 +2909,13 @@
       <c r="E13" s="1"/>
       <c r="K13" s="15"/>
       <c r="R13" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -2912,10 +2928,10 @@
       <c r="E14" s="1"/>
       <c r="K14" s="15"/>
       <c r="W14" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -2928,10 +2944,10 @@
       <c r="E15" s="1"/>
       <c r="K15" s="15"/>
       <c r="W15" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -2944,7 +2960,7 @@
       <c r="E16" s="1"/>
       <c r="K16" s="15"/>
       <c r="W16" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -2960,7 +2976,7 @@
       <c r="E17" s="1"/>
       <c r="K17" s="15"/>
       <c r="W17" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -2992,7 +3008,7 @@
       <c r="E19" s="1"/>
       <c r="K19" s="15"/>
       <c r="W19" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -3008,7 +3024,7 @@
       <c r="E20" s="1"/>
       <c r="K20" s="15"/>
       <c r="W20" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -3024,7 +3040,7 @@
       <c r="E21" s="1"/>
       <c r="K21" s="15"/>
       <c r="W21" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -3119,7 +3135,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ilEvpGmLo6a2O3ZAU+i9yQGGscrus6aYietO82VMOaIJdasi+nuCz4K4VGwvF5eoMx2reLQ9A/c/BCnrtsR9rw==" saltValue="4P2QQwj56WNptjDpbIU8kA==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KFe0QCuD87thpdz4ck4fKMGzw5Q53fIojp2KlnoFb1hbwe+Rkl3kkRpWu6YGCCD+TcLUYpZIHFUAvwG7q3nsPA==" saltValue="7iA+BZblGrXOgve/UNdGnw==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
